--- a/manuscript/submission_data/source_data/Source_Data_Figure_4.xlsx
+++ b/manuscript/submission_data/source_data/Source_Data_Figure_4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Panel_A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Panel_B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Panel_C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Panel_D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_D" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
@@ -495,7 +495,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aligned country programme timelines</t>
+          <t>Aligned country archive-context timelines</t>
         </is>
       </c>
     </row>
@@ -31107,7 +31107,7 @@
     <col width="36" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
@@ -31861,7 +31861,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>711</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -31871,7 +31871,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.018309859154929577</t>
+          <t>0.01828410689170183</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -32114,7 +32114,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.09090909090909091</t>
+          <t>0.07142857142857142</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -32288,7 +32288,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -32313,12 +32313,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -32328,7 +32328,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>promoted_from_screening; passes_stage1_default_epoch_rule; informative_but_bounds_wide</t>
+          <t>promoted_from_screening; passes_stage1_default_epoch_rule</t>
         </is>
       </c>
     </row>
@@ -32462,7 +32462,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -32472,7 +32472,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.07142857142857142</t>
+          <t>0.0425531914893617</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -32487,12 +32487,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -32502,7 +32502,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>passes_stage1_default_epoch_rule; informative_but_bounds_wide; prn_free_epoch</t>
+          <t>passes_stage1_default_epoch_rule; prn_free_epoch</t>
         </is>
       </c>
     </row>
@@ -32897,17 +32897,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>881</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>509</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.5870535714285714</t>
+          <t>0.5777525539160046</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -33498,12 +33498,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>711</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>136</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -33513,12 +33513,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.1770956316410862</t>
+          <t>0.17591499409681227</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.1617473435655254</t>
+          <t>0.16056670602125148</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -33714,12 +33714,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -33729,12 +33729,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0.4444444444444444</t>
+          <t>0.2777777777777778</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0.38888888888888884</t>
+          <t>0.22222222222222224</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -33858,12 +33858,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -33873,17 +33873,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.4666666666666667</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.4666666666666667</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -34002,12 +34002,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -34017,17 +34017,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.1346153846153846</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.46153846153846156</t>
+          <t>0.09615384615384615</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -34362,27 +34362,27 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>881</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.5723612622415669</t>
+          <t>0.5538628944504896</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>0.5973884657236126</t>
+          <t>0.5952121871599565</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0.02502720348204568</t>
+          <t>0.041349292709466856</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -42187,7 +42187,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
@@ -42254,7 +42254,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Architecture turnover between programme epochs</t>
+          <t>Architecture turnover between archive epochs</t>
         </is>
       </c>
     </row>
